--- a/Result/profitability/6113.xlsx
+++ b/Result/profitability/6113.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07250000000000001</v>
+        <v>0.01624999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.46875</v>
+        <v>14.56125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.98</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.18125</v>
+        <v>-0.1125</v>
       </c>
       <c r="N3" t="n">
-        <v>13.07875</v>
+        <v>12.62125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.19</v>
+        <v>-0.13</v>
       </c>
       <c r="N4" t="n">
-        <v>11.655</v>
+        <v>10.6375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.18375</v>
+        <v>-0.08375</v>
       </c>
       <c r="N5" t="n">
-        <v>9.8025</v>
+        <v>8.8675</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.12375</v>
+        <v>-0.04250000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>8.096250000000001</v>
+        <v>7.58875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.095</v>
+        <v>-0.005000000000000011</v>
       </c>
       <c r="N7" t="n">
-        <v>6.79125</v>
+        <v>6.37875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01875</v>
+        <v>0.03124999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>5.69375</v>
+        <v>5.30125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02874999999999999</v>
+        <v>0.02874999999999998</v>
       </c>
       <c r="N9" t="n">
         <v>4.7375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>278</v>
+      </c>
+      <c r="D75" t="n">
+        <v>243</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>31</v>
+      </c>
+      <c r="K75" t="n">
+        <v>31</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.06124999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.139999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2032362459546925</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.479999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3779686710459828</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
